--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_entertainment.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_entertainment.xlsx
@@ -588,37 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.242</v>
-      </c>
-      <c r="E2">
-        <v>0.154</v>
+        <v>-0.0493</v>
       </c>
       <c r="G2">
-        <v>-0.6423728813559322</v>
+        <v>-0.169811320754717</v>
       </c>
       <c r="H2">
-        <v>-0.7754237288135593</v>
+        <v>-0.2547169811320755</v>
       </c>
       <c r="I2">
-        <v>-0.8240088500698951</v>
+        <v>-0.196828972491411</v>
       </c>
       <c r="J2">
-        <v>-0.8240088500698951</v>
+        <v>-0.196828972491411</v>
       </c>
       <c r="K2">
-        <v>1.3</v>
+        <v>-3.69</v>
       </c>
       <c r="L2">
-        <v>0.05508474576271186</v>
+        <v>-0.08702830188679246</v>
       </c>
       <c r="M2">
-        <v>0.162</v>
+        <v>0.394</v>
       </c>
       <c r="N2">
-        <v>0.003446808510638298</v>
+        <v>0.01296052631578947</v>
       </c>
       <c r="O2">
-        <v>0.1246153846153846</v>
+        <v>-0.1067750677506775</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,82 +624,73 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.162</v>
+        <v>0.394</v>
       </c>
       <c r="T2">
         <v>1</v>
       </c>
       <c r="U2">
-        <v>90.40000000000001</v>
+        <v>28.5</v>
       </c>
       <c r="V2">
-        <v>1.923404255319149</v>
+        <v>0.9375</v>
       </c>
       <c r="W2">
-        <v>0.03672316384180791</v>
+        <v>-0.08785714285714286</v>
       </c>
       <c r="X2">
-        <v>0.1289953915345073</v>
+        <v>0.1085628311549043</v>
       </c>
       <c r="Y2">
-        <v>-0.09227222769269938</v>
-      </c>
-      <c r="Z2">
-        <v>0.6970278550391986</v>
-      </c>
-      <c r="AA2">
-        <v>-0.5743571212975356</v>
+        <v>-0.1964199740120471</v>
       </c>
       <c r="AB2">
-        <v>0.1276333495019988</v>
-      </c>
-      <c r="AC2">
-        <v>-0.7019904707995344</v>
+        <v>0.1030945342274972</v>
       </c>
       <c r="AD2">
-        <v>8.15</v>
+        <v>7.63</v>
       </c>
       <c r="AE2">
-        <v>0.05804430824763742</v>
+        <v>0.02774216817912934</v>
       </c>
       <c r="AF2">
-        <v>8.208044308247638</v>
+        <v>7.657742168179129</v>
       </c>
       <c r="AG2">
-        <v>-82.19195569175237</v>
+        <v>-20.84225783182087</v>
       </c>
       <c r="AH2">
-        <v>0.1486747884496503</v>
+        <v>0.2012137802168918</v>
       </c>
       <c r="AI2">
-        <v>0.07495380234481501</v>
+        <v>0.07881762170763139</v>
       </c>
       <c r="AJ2">
-        <v>2.335532483948171</v>
+        <v>-2.180667511748916</v>
       </c>
       <c r="AK2">
-        <v>-4.301432128052778</v>
+        <v>-0.3035674808642433</v>
       </c>
       <c r="AL2">
-        <v>0.747</v>
+        <v>0.646</v>
       </c>
       <c r="AM2">
-        <v>0.51</v>
+        <v>-1.484</v>
       </c>
       <c r="AN2">
-        <v>-0.5082631743062052</v>
+        <v>-1.145645645645646</v>
       </c>
       <c r="AO2">
-        <v>-26.10441767068273</v>
+        <v>-12.95665634674922</v>
       </c>
       <c r="AP2">
-        <v>5.125784576972396</v>
+        <v>3.129468142916047</v>
       </c>
       <c r="AQ2">
-        <v>-38.23529411764706</v>
+        <v>5.640161725067385</v>
       </c>
     </row>
     <row r="3">
@@ -722,37 +710,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.242</v>
-      </c>
-      <c r="E3">
-        <v>0.154</v>
+        <v>-0.0493</v>
       </c>
       <c r="G3">
-        <v>-0.6423728813559322</v>
+        <v>-0.169811320754717</v>
       </c>
       <c r="H3">
-        <v>-0.7754237288135593</v>
+        <v>-0.2547169811320755</v>
       </c>
       <c r="I3">
-        <v>-0.8240088500698951</v>
+        <v>-0.196828972491411</v>
       </c>
       <c r="J3">
-        <v>-0.8240088500698951</v>
+        <v>-0.196828972491411</v>
       </c>
       <c r="K3">
-        <v>1.3</v>
+        <v>-3.69</v>
       </c>
       <c r="L3">
-        <v>0.05508474576271186</v>
+        <v>-0.08702830188679246</v>
       </c>
       <c r="M3">
-        <v>0.162</v>
+        <v>0.394</v>
       </c>
       <c r="N3">
-        <v>0.003446808510638298</v>
+        <v>0.01296052631578947</v>
       </c>
       <c r="O3">
-        <v>0.1246153846153846</v>
+        <v>-0.1067750677506775</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -761,82 +746,73 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0.162</v>
+        <v>0.394</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>90.40000000000001</v>
+        <v>28.5</v>
       </c>
       <c r="V3">
-        <v>1.923404255319149</v>
+        <v>0.9375</v>
       </c>
       <c r="W3">
-        <v>0.03672316384180791</v>
+        <v>-0.08785714285714286</v>
       </c>
       <c r="X3">
-        <v>0.1289953915345073</v>
+        <v>0.1085628311549043</v>
       </c>
       <c r="Y3">
-        <v>-0.09227222769269938</v>
-      </c>
-      <c r="Z3">
-        <v>0.6970278550391986</v>
-      </c>
-      <c r="AA3">
-        <v>-0.5743571212975356</v>
+        <v>-0.1964199740120471</v>
       </c>
       <c r="AB3">
-        <v>0.1276333495019988</v>
-      </c>
-      <c r="AC3">
-        <v>-0.7019904707995344</v>
+        <v>0.1030945342274972</v>
       </c>
       <c r="AD3">
-        <v>8.15</v>
+        <v>7.63</v>
       </c>
       <c r="AE3">
-        <v>0.05804430824763742</v>
+        <v>0.02774216817912934</v>
       </c>
       <c r="AF3">
-        <v>8.208044308247638</v>
+        <v>7.657742168179129</v>
       </c>
       <c r="AG3">
-        <v>-82.19195569175237</v>
+        <v>-20.84225783182087</v>
       </c>
       <c r="AH3">
-        <v>0.1486747884496503</v>
+        <v>0.2012137802168918</v>
       </c>
       <c r="AI3">
-        <v>0.07495380234481501</v>
+        <v>0.07881762170763139</v>
       </c>
       <c r="AJ3">
-        <v>2.335532483948171</v>
+        <v>-2.180667511748916</v>
       </c>
       <c r="AK3">
-        <v>-4.301432128052778</v>
+        <v>-0.3035674808642433</v>
       </c>
       <c r="AL3">
-        <v>0.747</v>
+        <v>0.646</v>
       </c>
       <c r="AM3">
-        <v>0.51</v>
+        <v>-1.484</v>
       </c>
       <c r="AN3">
-        <v>-0.5082631743062052</v>
+        <v>-1.145645645645646</v>
       </c>
       <c r="AO3">
-        <v>-26.10441767068273</v>
+        <v>-12.95665634674922</v>
       </c>
       <c r="AP3">
-        <v>5.125784576972396</v>
+        <v>3.129468142916047</v>
       </c>
       <c r="AQ3">
-        <v>-38.23529411764706</v>
+        <v>5.640161725067385</v>
       </c>
     </row>
   </sheetData>
